--- a/sample_excel/Ren'Py版演出表格.xlsx
+++ b/sample_excel/Ren'Py版演出表格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\视觉小说项目\【表格演出工具】git仓库\sample_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D157A4-868E-4B1D-BD63-5265078BF322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77CCDE9D-5794-4F5B-9E9E-E496F068BB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sample_sheet" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <definedName name="SpriteList">OFFSET(参数表!$L$2,0,0,COUNTA(参数表!$L:$L)-1,1)</definedName>
     <definedName name="TransformList">OFFSET(参数表!$M$2,0,0,COUNTA(参数表!$M:$M)-1,1)</definedName>
     <definedName name="TransitionList">OFFSET(参数表!$N$2,0,0,COUNTA(参数表!$N:$N)-1,1)</definedName>
-    <definedName name="VarientList">OFFSET(参数表!$O$2,0,0,COUNTA(参数表!$O:$O)-1,1)</definedName>
+    <definedName name="VariantList">OFFSET(参数表!$O$2,0,0,COUNTA(参数表!$O:$O)-1,1)</definedName>
     <definedName name="VoiceList">OFFSET(参数表!$P$2,0,0,COUNTA(参数表!$P:$P)-1,1)</definedName>
     <definedName name="WarpList">OFFSET(参数表!$Q$2,0,0,COUNTA(参数表!$Q:$Q)-1,1)</definedName>
     <definedName name="WindowList">OFFSET(参数表!$R$2,0,0,COUNTA(参数表!$R:$R)-1,1)</definedName>
@@ -120,9 +120,6 @@
     <t>Event</t>
   </si>
   <si>
-    <t>EventVarient</t>
-  </si>
-  <si>
     <t>At</t>
   </si>
   <si>
@@ -159,9 +156,6 @@
     <t>Sprite</t>
   </si>
   <si>
-    <t>Varient</t>
-  </si>
-  <si>
     <t>Atr1</t>
   </si>
   <si>
@@ -449,6 +443,14 @@
   </si>
   <si>
     <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Variant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EventVariant</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -938,41 +940,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BA22"/>
-  <sheetFormatPr defaultRowHeight="11.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="11.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="60.58203125" style="1" customWidth="1"/>
+    <col min="1" max="2" width="4.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="60.5546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="60.58203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="60.5546875" style="1" customWidth="1"/>
     <col min="6" max="11" width="8.6640625" style="6" customWidth="1"/>
-    <col min="12" max="12" width="8.58203125" style="8" customWidth="1"/>
-    <col min="13" max="13" width="12.58203125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="10.58203125" style="8" customWidth="1"/>
-    <col min="15" max="17" width="8.58203125" style="8" customWidth="1"/>
-    <col min="18" max="18" width="10.58203125" style="8" customWidth="1"/>
+    <col min="12" max="12" width="8.5546875" style="8" customWidth="1"/>
+    <col min="13" max="13" width="12.5546875" style="8" customWidth="1"/>
+    <col min="14" max="14" width="10.5546875" style="8" customWidth="1"/>
+    <col min="15" max="17" width="8.5546875" style="8" customWidth="1"/>
+    <col min="18" max="18" width="10.5546875" style="8" customWidth="1"/>
     <col min="19" max="22" width="8.6640625" style="2" customWidth="1"/>
-    <col min="23" max="23" width="10.58203125" style="2" customWidth="1"/>
+    <col min="23" max="23" width="10.5546875" style="2" customWidth="1"/>
     <col min="24" max="27" width="8.6640625" style="2" customWidth="1"/>
     <col min="28" max="30" width="8.6640625" style="7" customWidth="1"/>
-    <col min="31" max="31" width="12.58203125" style="7" customWidth="1"/>
+    <col min="31" max="31" width="12.5546875" style="7" customWidth="1"/>
     <col min="32" max="32" width="8.6640625" style="7" customWidth="1"/>
-    <col min="33" max="33" width="12.58203125" style="3" customWidth="1"/>
+    <col min="33" max="33" width="12.5546875" style="3" customWidth="1"/>
     <col min="34" max="40" width="8.6640625" style="3" customWidth="1"/>
-    <col min="41" max="43" width="10.58203125" style="3" customWidth="1"/>
-    <col min="44" max="44" width="10.58203125" style="7" customWidth="1"/>
-    <col min="45" max="46" width="12.58203125" style="7" customWidth="1"/>
-    <col min="47" max="47" width="16.58203125" style="7" customWidth="1"/>
-    <col min="48" max="48" width="20.58203125" style="7" customWidth="1"/>
-    <col min="49" max="49" width="10.58203125" style="4" customWidth="1"/>
+    <col min="41" max="43" width="10.5546875" style="3" customWidth="1"/>
+    <col min="44" max="44" width="10.5546875" style="7" customWidth="1"/>
+    <col min="45" max="46" width="12.5546875" style="7" customWidth="1"/>
+    <col min="47" max="47" width="16.5546875" style="7" customWidth="1"/>
+    <col min="48" max="48" width="20.5546875" style="7" customWidth="1"/>
+    <col min="49" max="49" width="10.5546875" style="4" customWidth="1"/>
     <col min="50" max="50" width="8.6640625" style="4" customWidth="1"/>
-    <col min="51" max="51" width="10.58203125" style="4" customWidth="1"/>
-    <col min="52" max="52" width="10.58203125" style="9" customWidth="1"/>
-    <col min="53" max="53" width="10.58203125" style="5" customWidth="1"/>
+    <col min="51" max="51" width="10.5546875" style="4" customWidth="1"/>
+    <col min="52" max="52" width="10.5546875" style="9" customWidth="1"/>
+    <col min="53" max="53" width="10.5546875" style="5" customWidth="1"/>
     <col min="54" max="86" width="8.6640625" style="1" customWidth="1"/>
     <col min="87" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -983,7 +985,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -1040,215 +1042,215 @@
         <v>21</v>
       </c>
       <c r="W1" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="X1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="7" t="s">
+      <c r="AC1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="7" t="s">
+      <c r="AD1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="7" t="s">
+      <c r="AE1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="7" t="s">
+      <c r="AF1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="7" t="s">
+      <c r="AG1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AK1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AR1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AS1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="7" t="s">
+      <c r="AT1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="7" t="s">
+      <c r="AU1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="7" t="s">
+      <c r="AV1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="7" t="s">
+      <c r="AW1" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="7" t="s">
+      <c r="AX1" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="4" t="s">
+      <c r="AY1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="4" t="s">
+      <c r="AZ1" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="4" t="s">
+      <c r="BA1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="I5" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J6" s="6">
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I7" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O9" s="8">
         <v>1.2</v>
@@ -1260,124 +1262,124 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="U10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y10" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="X10" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y10" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="Z10" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AA10" s="2">
         <v>1</v>
       </c>
       <c r="AB10" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC10" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AD10" s="7">
         <v>5</v>
       </c>
       <c r="AE10" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="AH13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AP13" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AJ13" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN13" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AO13" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP13" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="AR13" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AT13" s="7">
         <v>5.5</v>
       </c>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="AG14" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AH14" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AJ14" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
       <c r="C15" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AW15" s="4" t="b">
         <v>1</v>
       </c>
       <c r="AX15" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AY15" s="4">
         <v>2</v>
@@ -1386,90 +1388,90 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AI16" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AK16" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AL16" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AM16" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="AL16" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AM16" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="AR16" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:53" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="AR17" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AT17" s="7">
         <v>2</v>
       </c>
       <c r="AU17" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:53" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="AR18" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:53" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="AR19" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AS19" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV19" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="AS19" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="AV19" s="7" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:53" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="BA20" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="21" spans="1:53" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="BA21" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:53" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:53" x14ac:dyDescent="0.25">
       <c r="C22" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1530,7 +1532,7 @@
       <formula1>SpriteList</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ1048576" xr:uid="{00000000-0002-0000-0000-000010000000}">
-      <formula1>VarientList</formula1>
+      <formula1>VariantList</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1540,15 +1542,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R8"/>
-  <sheetFormatPr defaultColWidth="16.58203125" defaultRowHeight="11.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="16.5546875" defaultRowHeight="11.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="19" width="16.58203125" style="10" customWidth="1"/>
-    <col min="20" max="16384" width="16.58203125" style="10"/>
+    <col min="1" max="19" width="16.5546875" style="10" customWidth="1"/>
+    <col min="20" max="16384" width="16.5546875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>6</v>
@@ -1560,7 +1562,7 @@
         <v>11</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F1" s="10" t="s">
         <v>19</v>
@@ -1569,7 +1571,7 @@
         <v>21</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I1" s="10" t="s">
         <v>5</v>
@@ -1581,177 +1583,177 @@
         <v>3</v>
       </c>
       <c r="L1" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N1" s="10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="O1" s="10" t="s">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="P1" s="10" t="s">
         <v>10</v>
       </c>
       <c r="Q1" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="R1" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="D2" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="G2" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2" s="10" t="s">
+      <c r="K2" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q4" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="R4" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q5" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
         <v>74</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="R2" s="10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q3" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="R3" s="10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="M4" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="N4" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q4" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R4" s="10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="M5" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="N5" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q5" s="10" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="N6" s="10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>
